--- a/Result/checksun_type/近眼顯示(Dear-Eye Display).xlsx
+++ b/Result/checksun_type/近眼顯示(Dear-Eye Display).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>41.82</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>44.24</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>48.88</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>48.88</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>13866223.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>14006133.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>14006133.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>12648509.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>24320696.58</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>24320696.58</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-7775.681584024802</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>13866223</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>13866223.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>41.33</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>44.46</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>49.11</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49.11</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>29444731.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>13396437.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>13396437.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>15603287.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>26176334.2</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>26176334.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>62018.19883899577</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>29444731</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>29444731.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>41.15</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>44.72</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>5812770.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>10126744.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>10126744.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>13659462.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>26334778.56</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>26334778.56</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1509617.050515225</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>5812770</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>5812770.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>41.65</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>45.12</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>49.74</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>49.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>11652789.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>10039474.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>10039474.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>14090576.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>28022915.42</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>28022915.42</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1168899.547788568</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>11652789</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>11652789.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>42.49</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>50.13</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>50.13</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>9254154.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>10142828.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>10142828.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>14282953.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>29323837.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>29323837.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1266130.167186609</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>9254154</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>9254154.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>43.2</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>50.51</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>50.51</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>10817743.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>11290885.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>11290885.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>14088287.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>30846889.58</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>30846889.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1102815.510355718</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>10817743</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>10817743.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>44.29</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>46.39</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>46.39</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>50.92</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>13096267.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>17810137.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>17810137.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>14094650.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>35046372.82</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>35046372.82</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-997649.9823703133</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>13096267</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>13096267.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>44.77</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>51.32</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>51.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>5376420.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>17192180.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>17192180.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>14173411.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>41560575.68</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>41560575.68</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-1055910.72873508</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>5376420</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>5376420.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>44.86</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>46.98</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>51.68</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>51.68</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>12169558.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>18141678.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>18141678.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>14783110.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>63447588.58</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>63447588.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-274302.804658493</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>12169558</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>12169558.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>44.92</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>47.21</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>51.98</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>47.21</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>51.98</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>14994438.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>18423078.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>18423078.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>14824346.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>70558395.84</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>70558395.84</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>124240.2584744319</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>14994438</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>14994438.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>45.03</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>52.28</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>52.28</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>43414004.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>16885689.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>16885689.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>15139529.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>72385410.04</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>72385410.04000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>386484.6251473799</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>43414004</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>43414004.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>88.82</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>89.97</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>101.54</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>101.54</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1496761.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1187172.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1187172.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1020894.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2058125.44</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2058125.44</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-65418.32762892707</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1496761</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1496761.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>85.55999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>89.42</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>101.99</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>89.42</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>101.99</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2115557.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>993448.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>993448.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>962655.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2145653.4</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2145653.4</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-98962.45567306643</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2115557</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2115557.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>84.28</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>89.54</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>102.79</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>102.79</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1396196.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>797567.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>797567.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>869667.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>2222751.52</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>2222751.52</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-209647.8366049416</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1396196</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1396196.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>84.74</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>90.4</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>103.48</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>103.48</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>446832.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>676255.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>676255.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>836932.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>2237649.02</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>2237649.02</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-283207.9937717296</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>446832</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>446832.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>86.17999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>91.23</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>104.22</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>104.22</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>480517.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>810164.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>810164.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>921369.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>2333587.64</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>2333587.64</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-276461.7899467224</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>480517</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>480517.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>87.38000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>91.96</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>105.02</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>105.02</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>528139.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>854615.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>854615.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1048562.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>2414824.58</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>2414824.58</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-260559.8276986149</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>528139</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>528139.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>89.12</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>92.97</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>105.91</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>92.97</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>105.91</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1136155.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>931861.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>931861.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1494189.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>2699451.5</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>2699451.5</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-233639.3877835108</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1136155</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1136155.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>90.53999999999999</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>93.86</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>106.84</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>93.86</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>106.84</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>789636.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>941766.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>941766.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1903952.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>2858383.84</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>2858383.84</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-251981.9240553796</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>789636</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>789636.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>107.48</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>107.48</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>1116375.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>997608.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>997608.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>2034960.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2909917.96</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2909917.96</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-232059.1571560712</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1116375</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1116375.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>91.28</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>95.66</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>108.04</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>95.66</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>108.04</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>702772.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1032573.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1032573.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>2004573.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>3051992.38</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>3051992.38</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-230317.9845443424</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>702772</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>702772.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>92.0</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>96.23</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>108.66</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>96.23</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>108.66</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>914371.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1242510.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1242510.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>2031632.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>3137803.82</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>3137803.82</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-175290.3456510033</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>914371</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>914371.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10463,11 +10331,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>2459</t>
@@ -10649,41 +10513,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr">
         <is>
           <t>0</t>
@@ -10704,20 +10564,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>0</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10590,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>0</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>

--- a/Result/checksun_type/近眼顯示(Dear-Eye Display).xlsx
+++ b/Result/checksun_type/近眼顯示(Dear-Eye Display).xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>611.933</t>
+          <t>393.09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-18.40</t>
+          <t>-19.18</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>60.61</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>49.49</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.36</v>
+        <v>0.67</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.41</v>
+        <v>-0.67</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>46.23999999999999</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>46.56</v>
+        <v>46.55</v>
       </c>
       <c r="BA2" t="n">
-        <v>45.55</v>
+        <v>45.5</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-12.96</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="BD2" t="n">
         <v>0.21</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-94.83</t>
+          <t>-94.98</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>140985644.6405941</t>
+          <t>140761964.4100791</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>28909914.0</t>
+          <t>18535632.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>12002975.6</v>
+        <v>13786227</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>8407947.6</t>
+          <t>10089304.9</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>11349631.46</v>
+        <v>11544281.4</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>3595028</t>
+          <t>3696922</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-531224.1277653989</t>
+          <t>-204450.8838703186</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>1219630.41165166</t>
+          <t>1592801.957552623</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>28909914.0</t>
+          <t>18535632.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>83.56</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>183.989</t>
+          <t>611.933</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>21.78</t>
+          <t>42.76</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-20.92</t>
+          <t>-18.40</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,63 +1631,63 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.37</v>
+        <v>-0.41</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-6.14</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>46.35</t>
+          <t>46.37</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>46.52</v>
+        <v>46.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>45.6</v>
+        <v>45.55</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>48.58</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-32.80</t>
+          <t>-12.96</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="BE3" t="n">
         <v>0.25</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-94.66</t>
+          <t>-94.83</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>140985644.6405941</t>
+          <t>140761964.4100791</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>8425051.0</t>
+          <t>28909914.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>7194349.4</v>
+        <v>12002975.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>5907553.5</t>
+          <t>8407947.6</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>10979132.72</v>
+        <v>11349631.46</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1286795</t>
+          <t>3595028</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-849561.3167503187</t>
+          <t>-531224.1277653989</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-468560.2400515648</t>
+          <t>1219630.41165166</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>8425051.0</t>
+          <t>28909914.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>83.56</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>45.55</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>167.921</t>
+          <t>183.989</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,149 +1937,149 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>45.55</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>21.78</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-08-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-08-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>59.1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>57.6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-20.92</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>8.84</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/05/29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/09/30</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/03/20</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/31</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
           <t>45.6</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>8.72</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-08-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-08-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-08-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>59.1</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>57.6</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>57.8</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-20.83</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>8.84</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/05/29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/09/30</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/03/20</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/31</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>2025/11/18</t>
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2133,51 +2133,51 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-2.23</v>
+        <v>-1.73</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.28</v>
+        <v>-0.37</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-6.35</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>46.35</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>46.51</v>
+        <v>46.52</v>
       </c>
       <c r="BA4" t="n">
-        <v>45.68</v>
+        <v>45.6</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>48.78</t>
+          <t>48.58</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-32.80</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-94.22</t>
+          <t>-94.66</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>140985644.6405941</t>
+          <t>140761964.4100791</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>7764928.0</t>
+          <t>8425051.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>6713271</v>
+        <v>7194349.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>6174809.9</t>
+          <t>5907553.5</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>11130847.42</v>
+        <v>10979132.72</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>538461</t>
+          <t>1286795</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-918834.2397864558</t>
+          <t>-849561.3167503187</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-668720.1267686123</t>
+          <t>-468560.2400515648</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>7764928.0</t>
+          <t>8425051.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>83.56</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>113.458</t>
+          <t>167.921</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-19.27</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,208 +2605,208 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>73.31</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.77</v>
+        <v>-2.23</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.89</v>
+        <v>0.28</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>-6.35</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>46.64</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>48.78</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-5.28</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-94.22</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>140761964.4100791</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>7764928.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>6713271</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>6174809.9</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
+        <v>11130847.42</v>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>538461</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-918834.2397864558</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-668720.1267686123</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>7764928.0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>2025/12/24</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>-2.98</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>澤米</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>澤米</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>13.55184581976113</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>-37.24379770097699</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>-19.37313712081134</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>-6.62</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>46.86</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>46.45</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>45.74</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>48.99</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>31.39</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-94.14</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>140985644.6405941</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>5295610.0</t>
-        </is>
-      </c>
-      <c r="BK5" t="n">
-        <v>5975177</v>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>6355832.2</t>
-        </is>
-      </c>
-      <c r="BM5" t="n">
-        <v>11167704.16</v>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-380655</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-964309.5330624273</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-860052.4961226573</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>5295610.0</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>47.0</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>2025/12/24</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>澤米</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>澤米</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>13.55184581976113</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>-37.24379770097699</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>-19.37313712081134</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="CH5" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
       <c r="CI5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>83.56</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>202.022</t>
+          <t>113.458</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-18.06</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,87 +3071,87 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>88.41</t>
+          <t>73.31</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.45</v>
+        <v>-0.77</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.44</v>
+        <v>0.89</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-6.62</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.86</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>46.32</v>
+        <v>46.45</v>
       </c>
       <c r="BA6" t="n">
-        <v>45.79</v>
+        <v>45.74</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-94.60</t>
+          <t>-94.14</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>140985644.6405941</t>
+          <t>140761964.4100791</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>9619375.0</t>
+          <t>5295610.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>6392382.8</v>
+        <v>5975177</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>6208497.1</t>
+          <t>6355832.2</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>11274537.98</v>
+        <v>11167704.16</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>183885</t>
+          <t>-380655</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-983265.3579605673</t>
+          <t>-964309.5330624273</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-838098.5060526272</t>
+          <t>-860052.4961226573</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>9619375.0</t>
+          <t>5295610.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>83.56</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>104.026</t>
+          <t>202.022</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.96</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-18.58</t>
+          <t>-18.06</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>75.36</t>
+          <t>88.41</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-7.10</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>46.19</v>
+        <v>46.32</v>
       </c>
       <c r="BA7" t="n">
-        <v>45.82</v>
+        <v>45.79</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>49.32</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>70.46</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-95.38</t>
+          <t>-94.60</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>140985644.6405941</t>
+          <t>140761964.4100791</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>4866783.0</t>
+          <t>9619375.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>4812919.6</v>
+        <v>6392382.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>6013258.0</t>
+          <t>6208497.1</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>11442475.58</v>
+        <v>11274537.98</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1200338</t>
+          <t>183885</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1009659.331034738</t>
+          <t>-983265.3579605673</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-1240064.109307848</t>
+          <t>-838098.5060526272</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>4866783.0</t>
+          <t>9619375.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>83.56</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>127.552</t>
+          <t>104.026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-30.53</t>
+          <t>-19.96</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-18.40</t>
+          <t>-18.58</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>82.61</t>
+          <t>75.36</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.79</v>
+        <v>0.19</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-7.10</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>46</v>
+        <v>46.19</v>
       </c>
       <c r="BA8" t="n">
-        <v>45.86</v>
+        <v>45.82</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>49.49</t>
+          <t>49.32</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>100.39</t>
+          <t>70.46</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-96.19</t>
+          <t>-95.38</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>140985644.6405941</t>
+          <t>140761964.4100791</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>6019659.0</t>
+          <t>4866783.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>4620757.6</v>
+        <v>4812919.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>6651336.6</t>
+          <t>6013258.0</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>11617664.06</v>
+        <v>11442475.58</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2030579</t>
+          <t>-1200338</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-967767.5531669002</t>
+          <t>-1009659.331034738</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-1260806.395768597</t>
+          <t>-1240064.109307848</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>6019659.0</t>
+          <t>4866783.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>83.56</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.35</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
           <t>46.9</t>
-        </is>
-      </c>
-      <c r="CT8" t="inlineStr">
-        <is>
-          <t>47.0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>86.938</t>
+          <t>127.552</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.11</t>
+          <t>-30.53</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-18.92</t>
+          <t>-18.40</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,87 +4532,87 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>86.96</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>64.15</t>
+          <t>82.61</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.32</v>
+        <v>0.79</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>45.82</v>
+        <v>46</v>
       </c>
       <c r="BA9" t="n">
-        <v>45.89</v>
+        <v>45.86</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>49.66</t>
+          <t>49.49</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>145.03</t>
+          <t>100.39</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-97.15</t>
+          <t>-96.19</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>140985644.6405941</t>
+          <t>140761964.4100791</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>4074458.0</t>
+          <t>6019659.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>5636348.8</v>
+        <v>4620757.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>8554374.1</t>
+          <t>6651336.6</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>12032756.92</v>
+        <v>11617664.06</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-2918025</t>
+          <t>-2030579</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-914487.7636029553</t>
+          <t>-967767.5531669002</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-1368931.862292217</t>
+          <t>-1260806.395768597</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>4074458.0</t>
+          <t>6019659.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>83.56</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>156.072</t>
+          <t>86.938</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-23.80</t>
+          <t>-34.11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-18.14</t>
+          <t>-18.92</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>64.15</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.33</v>
+        <v>0.32</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.58</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>46.55</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>45.64</v>
+        <v>45.82</v>
       </c>
       <c r="BA10" t="n">
-        <v>45.95</v>
+        <v>45.89</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>49.66</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>269.06</t>
+          <t>145.03</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-98.18</t>
+          <t>-97.15</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>140985644.6405941</t>
+          <t>140761964.4100791</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>7381639.0</t>
+          <t>4074458.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>6736487.4</v>
+        <v>5636348.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>8840880.9</t>
+          <t>8554374.1</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>12370166.28</v>
+        <v>12032756.92</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-2104393</t>
+          <t>-2918025</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-831861.5638412713</t>
+          <t>-914487.7636029553</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-1266091.997958381</t>
+          <t>-1368931.862292217</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>7381639.0</t>
+          <t>4074458.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>80.37</t>
+          <t>83.56</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>47.15</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>46.65</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5699.0</t>
+          <t>4746.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,149 +5346,149 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-6.21</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-07-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-03-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-03-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>119.5</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-27.62</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8.22</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024/12/10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/02/12</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
           <t>84.9</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>17.09</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-07-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-03-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-03-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>119.5</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>73.0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-28.95</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024/12/10</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>77.2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/02/12</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>78.7</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>84.9</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
           <t>2025/12/16</t>
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-2.93</v>
+        <v>0.19</v>
       </c>
       <c r="AV11" t="n">
-        <v>-1.39</v>
+        <v>-2.35</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-8.57</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>87.46000000000001</t>
+          <t>86.34</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>88.7</v>
+        <v>88.42</v>
       </c>
       <c r="BA11" t="n">
-        <v>90.3</v>
+        <v>90.05</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>98.77</t>
+          <t>98.36</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-11.55</t>
+          <t>-9.79</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-1.35</v>
+        <v>-1.36</v>
       </c>
       <c r="BE11" t="n">
-        <v>-1.21</v>
+        <v>-1.24</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-110.08</t>
+          <t>-110.34</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1199847.889655172</t>
+          <t>1199044.57231405</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>488190.0</t>
+          <t>411093.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>1018674.8</v>
+        <v>804665.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>869960.2</t>
+          <t>857971.9</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>1235131.72</v>
+        <v>1223916.62</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>148714</t>
+          <t>-53306</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-36640.62980323846</t>
+          <t>-38095.90699665501</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-20336.80084912281</t>
+          <t>-46099.93156044604</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>488190.0</t>
+          <t>411093.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>27.21</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>93.01</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5766,27 +5766,27 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4517.0</t>
+          <t>5699.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-27.53</t>
+          <t>-28.95</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.97</v>
+        <v>-2.93</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.86</v>
+        <v>-1.39</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-8.57</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>87.46000000000001</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>89.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>90.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>99.28</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-11.55</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-1.15</v>
+        <v>-1.35</v>
       </c>
       <c r="BE12" t="n">
-        <v>-1.18</v>
+        <v>-1.21</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-109.79</t>
+          <t>-110.08</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1199847.889655172</t>
+          <t>1199044.57231405</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>393125.0</t>
+          <t>488190.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>1007832.8</v>
+        <v>1018674.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>844744.2</t>
+          <t>869960.2</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>1254190.86</v>
+        <v>1235131.72</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>163088</t>
+          <t>148714</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-39604.96234035039</t>
+          <t>-36640.62980323846</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>8933.593054521945</t>
+          <t>-20336.80084912281</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>393125.0</t>
+          <t>488190.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>93.01</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6253,27 +6253,27 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7033.0</t>
+          <t>4517.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-28.03</t>
+          <t>-27.53</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,63 +6501,63 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-3.41</v>
+        <v>-1.97</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.43</v>
+        <v>-0.86</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>89.03999999999999</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>89.42</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="BA13" t="n">
-        <v>90.95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>99.28</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>10.62</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-1.06</v>
+        <v>-1.15</v>
       </c>
       <c r="BE13" t="n">
         <v>-1.18</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-109.84</t>
+          <t>-109.79</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>1199847.889655172</t>
+          <t>1199044.57231405</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>608192.0</t>
+          <t>393125.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>1086968.4</v>
+        <v>1007832.8</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>833474.0</t>
+          <t>844744.2</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>1262665.78</v>
+        <v>1254190.86</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>253494</t>
+          <t>163088</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-48430.15423032719</t>
+          <t>-39604.96234035039</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>60614.92030778143</t>
+          <t>8933.593054521945</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>608192.0</t>
+          <t>393125.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>26.47</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>93.01</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6740,27 +6740,27 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
           <t>88.0</t>
         </is>
       </c>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23549.0</t>
+          <t>7033.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>53.66</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-26.61</t>
+          <t>-28.03</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>20.92</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-7.98</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>71.59</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-2.6</v>
+        <v>-3.41</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.38</v>
+        <v>-0.43</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>90.03999999999999</t>
+          <t>89.03999999999999</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>89.7</v>
+        <v>89.42</v>
       </c>
       <c r="BA14" t="n">
-        <v>91.28</v>
+        <v>90.95</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>100.36</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>29.37</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.86</v>
+        <v>-1.06</v>
       </c>
       <c r="BE14" t="n">
-        <v>-1.21</v>
+        <v>-1.18</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-110.10</t>
+          <t>-109.84</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>1199847.889655172</t>
+          <t>1199044.57231405</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>2122726.0</t>
+          <t>608192.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>1271524.8</v>
+        <v>1086968.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>827510.9</t>
+          <t>833474.0</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>1267007.76</v>
+        <v>1262665.78</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>444013</t>
+          <t>253494</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-68256.5314190742</t>
+          <t>-48430.15423032719</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>109237.6763728742</t>
+          <t>60614.92030778143</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>2122726.0</t>
+          <t>608192.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>26.47</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>93.01</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7227,27 +7227,27 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15899.0</t>
+          <t>23549.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>53.66</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-22.93</t>
+          <t>-26.61</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>20.92</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-7.98</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>86.46</t>
+          <t>71.59</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>1.93</v>
+        <v>-2.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-9.04</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>90.36</t>
+          <t>90.03999999999999</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>89.94</v>
+        <v>89.7</v>
       </c>
       <c r="BA15" t="n">
-        <v>91.61</v>
+        <v>91.28</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>100.76</t>
+          <t>100.36</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>29.37</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.76</v>
+        <v>-0.86</v>
       </c>
       <c r="BE15" t="n">
-        <v>-1.3</v>
+        <v>-1.21</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-110.85</t>
+          <t>-110.10</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>1199847.889655172</t>
+          <t>1199044.57231405</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>1481141.0</t>
+          <t>2122726.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>911278.6</v>
+        <v>1271524.8</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>656854.7</t>
+          <t>827510.9</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>1254226.66</v>
+        <v>1267007.76</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>254423</t>
+          <t>444013</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-100528.2055630648</t>
+          <t>-68256.5314190742</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>12525.91088111838</t>
+          <t>109237.6763728742</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>1481141.0</t>
+          <t>2122726.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>35.44</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>93.01</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7714,27 +7714,27 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4861.0</t>
+          <t>15899.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-22.93</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,17 +7962,17 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>73.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
@@ -7981,47 +7981,47 @@
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.18</v>
+        <v>1.93</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.58</v>
+        <v>0.47</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>90.36</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>89.98</v>
+        <v>89.94</v>
       </c>
       <c r="BA16" t="n">
-        <v>91.95</v>
+        <v>91.61</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>101.07</t>
+          <t>100.76</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>41.41</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-1.08</v>
+        <v>-0.76</v>
       </c>
       <c r="BE16" t="n">
-        <v>-1.44</v>
+        <v>-1.3</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-111.97</t>
+          <t>-110.85</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>1199847.889655172</t>
+          <t>1199044.57231405</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>433980.0</t>
+          <t>1481141.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>721245.6</v>
+        <v>911278.6</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>536973.1</t>
+          <t>656854.7</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>1297321.12</v>
+        <v>1254226.66</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>184272</t>
+          <t>254423</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-121083.4994620072</t>
+          <t>-100528.2055630648</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-57339.85806714394</t>
+          <t>12525.91088111838</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>433980.0</t>
+          <t>1481141.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>35.44</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>93.01</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8201,27 +8201,27 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="CS16" t="inlineStr">
+        <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="CS16" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8620.0</t>
+          <t>4861.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.12</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-24.60</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>85.94</t>
+          <t>73.44</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>93.31</t>
+          <t>86.46</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>1.78</v>
+        <v>-0.18</v>
       </c>
       <c r="AV17" t="n">
-        <v>-1.93</v>
+        <v>-0.58</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>88.52000000000001</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>90.27</v>
+        <v>89.98</v>
       </c>
       <c r="BA17" t="n">
-        <v>92.22</v>
+        <v>91.95</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>101.49</t>
+          <t>101.07</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>22.40</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-1.18</v>
+        <v>-1.08</v>
       </c>
       <c r="BE17" t="n">
-        <v>-1.53</v>
+        <v>-1.44</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-112.71</t>
+          <t>-111.97</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>1199847.889655172</t>
+          <t>1199044.57231405</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>788803.0</t>
+          <t>433980.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>681655.6</v>
+        <v>721245.6</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>532930.9</t>
+          <t>536973.1</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>1334873.04</v>
+        <v>1297321.12</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>148724</t>
+          <t>184272</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-132673.2524428914</t>
+          <t>-121083.4994620072</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-42904.42591940647</t>
+          <t>-57339.85806714394</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>788803.0</t>
+          <t>433980.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>32.50</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>93.01</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8688,27 +8688,27 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="CR17" t="inlineStr">
-        <is>
-          <t>93.5</t>
-        </is>
-      </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16680.0</t>
+          <t>8620.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-24.60</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.94</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>78.18</t>
+          <t>93.31</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>3.86</v>
+        <v>1.78</v>
       </c>
       <c r="AV18" t="n">
-        <v>-3.46</v>
+        <v>-1.93</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-9.19</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>87.61999999999999</t>
+          <t>88.52000000000001</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>90.76000000000001</v>
+        <v>90.27</v>
       </c>
       <c r="BA18" t="n">
-        <v>92.52</v>
+        <v>92.22</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>101.88</t>
+          <t>101.49</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-1.38</v>
+        <v>-1.18</v>
       </c>
       <c r="BE18" t="n">
-        <v>-1.61</v>
+        <v>-1.53</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-113.42</t>
+          <t>-112.71</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>1199847.889655172</t>
+          <t>1199044.57231405</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>1530974.0</t>
+          <t>788803.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>579979.6</v>
+        <v>681655.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>518134.7</t>
+          <t>532930.9</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>1377293.78</v>
+        <v>1334873.04</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>61844</t>
+          <t>148724</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-148994.8572653433</t>
+          <t>-132673.2524428914</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-58766.82906837412</t>
+          <t>-42904.42591940647</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>1530974.0</t>
+          <t>788803.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>32.50</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>93.01</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9175,27 +9175,27 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9217,7 +9217,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3593.0</t>
+          <t>16680.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>14.82</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>78.18</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>2.98</v>
+        <v>3.86</v>
       </c>
       <c r="AV19" t="n">
-        <v>-4.45</v>
+        <v>-3.46</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.19</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>86.72</t>
+          <t>87.61999999999999</t>
         </is>
       </c>
       <c r="AZ19" t="n">
         <v>90.76000000000001</v>
       </c>
       <c r="BA19" t="n">
-        <v>93.03</v>
+        <v>92.52</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>102.29</t>
+          <t>101.88</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-1.7</v>
+        <v>-1.38</v>
       </c>
       <c r="BE19" t="n">
-        <v>-1.67</v>
+        <v>-1.61</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-113.90</t>
+          <t>-113.42</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>1199847.889655172</t>
+          <t>1199044.57231405</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>321495.0</t>
+          <t>1530974.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>383497</v>
+        <v>579979.6</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>421816.7</t>
+          <t>518134.7</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>1399030.72</v>
+        <v>1377293.78</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-38319</t>
+          <t>61844</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-165399.9533011559</t>
+          <t>-148994.8572653433</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-158846.9111001717</t>
+          <t>-58766.82906837412</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>321495.0</t>
+          <t>1530974.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>91.29</t>
+          <t>93.01</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9662,27 +9662,27 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>光電業平上櫃</t>
+          <t>光電業右上上櫃</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9704,7 +9704,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>42.563</t>
+          <t>77.418</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>68.13</t>
+          <t>-42.63</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,12 +9910,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -9929,47 +9929,47 @@
         </is>
       </c>
       <c r="AU20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AV20" t="n">
         <v>0.49</v>
       </c>
-      <c r="AV20" t="n">
-        <v>0.21</v>
-      </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>65.88000000000001</t>
+          <t>66.08000000000001</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>65.73999999999999</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="BA20" t="n">
-        <v>65.79000000000001</v>
+        <v>65.83</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>64.98</t>
+          <t>65.01</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>147.04</t>
+          <t>326.06</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-103.08</t>
+          <t>-101.70</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,48 +9988,48 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>7654469.433103449</t>
+          <t>7654531.076446281</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>2812040.0</t>
+          <t>5132815.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>9138992.4</v>
+        <v>3358919.2</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>5435745.3</t>
+          <t>5854617.6</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>4709548.48</v>
+        <v>4422973.48</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>3703247</t>
+          <t>-2495698</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>380500.4289775711</t>
+          <t>355170.1455081891</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>252997.431735809</t>
+          <t>215853.5864265878</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>2812040.0</t>
+          <t>5132815.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
@@ -10154,17 +10154,17 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
@@ -10191,7 +10191,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>50.174</t>
+          <t>42.563</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>68.13</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -10397,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10416,47 +10416,47 @@
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>0.82</v>
+        <v>0.49</v>
       </c>
       <c r="AV21" t="n">
-        <v>-0.09</v>
+        <v>0.21</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>65.88000000000001</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>65.72</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="BA21" t="n">
-        <v>65.75</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>64.96</t>
+          <t>64.98</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>61.56</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-104.21</t>
+          <t>-103.08</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,48 +10475,48 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>7654469.433103449</t>
+          <t>7654531.076446281</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>3319853.0</t>
+          <t>2812040.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>8867639.4</v>
+        <v>9138992.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>5255348.3</t>
+          <t>5435745.3</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>4744393.16</v>
+        <v>4709548.48</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>3612291</t>
+          <t>3703247</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>403682.792112437</t>
+          <t>380500.4289775711</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>545678.9096155614</t>
+          <t>252997.431735809</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>3319853.0</t>
+          <t>2812040.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
@@ -10641,17 +10641,17 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
@@ -10678,7 +10678,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>40.517</t>
+          <t>50.174</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>65.29</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10899,51 +10899,51 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="AV22" t="n">
-        <v>-0.44</v>
+        <v>-0.09</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>65.44000000000001</t>
+          <t>65.66</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>65.73</v>
+        <v>65.72</v>
       </c>
       <c r="BA22" t="n">
-        <v>65.70999999999999</v>
+        <v>65.75</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>64.94</t>
+          <t>64.96</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-13.39</t>
+          <t>61.56</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-104.86</t>
+          <t>-104.21</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>7654469.433103449</t>
+          <t>7654531.076446281</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>2684894.0</t>
+          <t>3319853.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>8627839.199999999</v>
+        <v>8867639.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>5219842.6</t>
+          <t>5255348.3</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>4773657.46</v>
+        <v>4744393.16</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>3407996</t>
+          <t>3612291</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>377865.316202778</t>
+          <t>403682.792112437</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>889898.2383860806</t>
+          <t>545678.9096155614</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>2684894.0</t>
+          <t>3319853.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,12 +11063,12 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>43.328</t>
+          <t>40.517</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,159 +11190,159 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>65.29</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>64.6</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2026/01/02</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>52.89</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>64.6</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2026/01/02</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
       <c r="AK23" t="inlineStr">
         <is>
           <t>2025-12-29 00:00:00</t>
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11386,48 +11386,48 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>50.96</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.55</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.65</v>
+        <v>-0.44</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>65.34</t>
+          <t>65.44000000000001</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>65.77</v>
+        <v>65.73</v>
       </c>
       <c r="BA23" t="n">
-        <v>65.67</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>64.91</t>
+          <t>64.94</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-105.80</t>
+          <t>-13.39</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="BE23" t="n">
         <v>-0.07000000000000001</v>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-104.70</t>
+          <t>-104.86</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>7654469.433103449</t>
+          <t>7654531.076446281</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>2844994.0</t>
+          <t>2684894.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>8397068.4</v>
+        <v>8627839.199999999</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>5492196.8</t>
+          <t>5219842.6</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>4801362.28</v>
+        <v>4773657.46</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>2904871</t>
+          <t>3407996</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>284768.4212603593</t>
+          <t>377865.316202778</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>1417889.378115891</t>
+          <t>889898.2383860806</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>2844994.0</t>
+          <t>2684894.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,17 +11550,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
+          <t>66.5</t>
+        </is>
+      </c>
+      <c r="CS23" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="CS23" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>521.983</t>
+          <t>43.328</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>57.23</t>
+          <t>52.89</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,38 +11858,38 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>50.96</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-0.21</v>
+        <v>0.55</v>
       </c>
       <c r="AV24" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.65</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -11898,26 +11898,26 @@
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>65.8</v>
+        <v>65.77</v>
       </c>
       <c r="BA24" t="n">
-        <v>65.64</v>
+        <v>65.67</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>64.88</t>
+          <t>64.91</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-244.72</t>
+          <t>-105.80</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-103.46</t>
+          <t>-104.70</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>7654469.433103449</t>
+          <t>7654531.076446281</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>34033181.0</t>
+          <t>2844994.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>8350316</v>
+        <v>8397068.4</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>5310919.1</t>
+          <t>5492196.8</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>4894753.42</v>
+        <v>4801362.28</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>3039396</t>
+          <t>2904871</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>78746.42910480825</t>
+          <t>284768.4212603593</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>2104369.957082909</t>
+          <t>1417889.378115891</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>34033181.0</t>
+          <t>2844994.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,17 +12037,17 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,42 +12149,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>521.983</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>65.2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>22.344</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-22.37</t>
+          <t>57.23</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,12 +12324,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -12345,38 +12345,38 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-0.37</v>
+        <v>-0.21</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.8</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -12385,26 +12385,26 @@
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>65.86</v>
+        <v>65.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>65.61</v>
+        <v>65.64</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>64.86</t>
+          <t>64.88</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-716.13</t>
+          <t>-244.72</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-101.34</t>
+          <t>-103.46</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>7654469.433103449</t>
+          <t>7654531.076446281</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>1455275.0</t>
+          <t>34033181.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>1732498.2</v>
+        <v>8350316</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>2231661.4</t>
+          <t>5310919.1</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>4596744.14</v>
+        <v>4894753.42</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-499163</t>
+          <t>3039396</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-289548.7578003009</t>
+          <t>78746.42910480825</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-331691.0357171679</t>
+          <t>2104369.957082909</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>1455275.0</t>
+          <t>34033181.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>65.2</t>
-        </is>
-      </c>
-      <c r="CS25" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>65.1</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>32.498</t>
+          <t>22.344</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-34.63</t>
+          <t>-22.37</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-0.31</v>
+        <v>-0.37</v>
       </c>
       <c r="AV26" t="n">
-        <v>-0.97</v>
+        <v>-0.8</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.34</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>65.94</v>
+        <v>65.86</v>
       </c>
       <c r="BA26" t="n">
-        <v>65.56</v>
+        <v>65.61</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>64.85</t>
+          <t>64.86</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-932.64</t>
+          <t>-716.13</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-98.94</t>
+          <t>-101.34</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>7654469.433103449</t>
+          <t>7654531.076446281</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>2120852.0</t>
+          <t>1455275.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>1643057.2</v>
+        <v>1732498.2</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>2513544.9</t>
+          <t>2231661.4</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>4602628.34</v>
+        <v>4596744.14</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-870487</t>
+          <t>-499163</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>-281886.5254517796</t>
+          <t>-289548.7578003009</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-309442.1312988084</t>
+          <t>-331691.0357171679</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>2120852.0</t>
+          <t>1455275.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>23.153</t>
+          <t>32.498</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-37.23</t>
+          <t>-34.63</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-01-06 00:00:00</t>
+          <t>2026-01-07 00:00:00</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>0.52</v>
+        <v>-0.31</v>
       </c>
       <c r="AV27" t="n">
-        <v>-1.15</v>
+        <v>-0.97</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>65.26000000000002</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>66.02</v>
+        <v>65.94</v>
       </c>
       <c r="BA27" t="n">
-        <v>65.51000000000001</v>
+        <v>65.56</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>64.84</t>
+          <t>64.85</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-269.66</t>
+          <t>-932.64</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-96.47</t>
+          <t>-98.94</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>7654469.433103449</t>
+          <t>7654531.076446281</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>1531040.0</t>
+          <t>2120852.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>1811846</v>
+        <v>1643057.2</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>2886610.3</t>
+          <t>2513544.9</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>4664357.06</v>
+        <v>4602628.34</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-1074764</t>
+          <t>-870487</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>-276876.4152977744</t>
+          <t>-281886.5254517796</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-337918.2988690515</t>
+          <t>-309442.1312988084</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>1531040.0</t>
+          <t>2120852.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>39.845</t>
+          <t>23.153</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,159 +13625,159 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-37.23</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-01-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-01-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>64.6</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2026/01/02</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-9.48</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2026-01-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>64.6</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2026/01/02</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
       <c r="AK28" t="inlineStr">
         <is>
           <t>2025-12-29 00:00:00</t>
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>0.8</v>
+        <v>0.52</v>
       </c>
       <c r="AV28" t="n">
-        <v>-1.34</v>
+        <v>-1.15</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>65.18</t>
+          <t>65.26000000000002</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>66.06</v>
+        <v>66.02</v>
       </c>
       <c r="BA28" t="n">
-        <v>65.45</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>64.82</t>
+          <t>64.84</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-200.47</t>
+          <t>-269.66</t>
         </is>
       </c>
       <c r="BD28" t="n">
         <v>-0.08</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-94.09</t>
+          <t>-96.47</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>7654469.433103449</t>
+          <t>7654531.076446281</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>2611232.0</t>
+          <t>1531040.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>2587325.2</v>
+        <v>1811846</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>2858282.3</t>
+          <t>2886610.3</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>4766658</v>
+        <v>4664357.06</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-270957</t>
+          <t>-1074764</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>-265777.8910120876</t>
+          <t>-276876.4152977744</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-303335.8847240754</t>
+          <t>-337918.2988690515</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>2611232.0</t>
+          <t>1531040.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CS28" t="inlineStr">
+        <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="CR28" t="inlineStr">
-        <is>
-          <t>65.8</t>
-        </is>
-      </c>
-      <c r="CS28" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
